--- a/data/sars/pacific/tables/Pacific_2005_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2005_Appendix3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30225630-E9BE-9449-8F0A-BF328B648400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AEB51F-DE44-5A4E-88DC-E32151C76DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7220" yWindow="500" windowWidth="28040" windowHeight="17440" xr2:uid="{F51D830C-6866-6540-B1B8-5FD9A206E5C1}"/>
+    <workbookView xWindow="36520" yWindow="500" windowWidth="15620" windowHeight="18740" xr2:uid="{F51D830C-6866-6540-B1B8-5FD9A206E5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="tabula-Pacific_2005_Appendix3" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="95">
   <si>
     <t>California sea lion</t>
   </si>
@@ -290,13 +290,28 @@
   </si>
   <si>
     <t>Dall's porpoise</t>
+  </si>
+  <si>
+    <t>RF=0.4 was a typo in table; actual SAR says 0.45</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.5 in SAR; RF=0.45 was typo in table</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -427,6 +442,13 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -773,9 +795,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1151,23 +1174,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E5A27D-4F7E-F840-9C2B-1D9E5F36A123}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -1175,69 +1200,75 @@
         <v>57</v>
       </c>
       <c r="C1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>62</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>65</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
       <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1">
         <v>138881</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.12</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>8333</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>1562</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>1476</v>
       </c>
-      <c r="K2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1245,209 +1276,212 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1">
         <v>31600</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.12</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>1896</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>67</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>389</v>
       </c>
-      <c r="K3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
       <c r="D4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>22380</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.12</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>1343</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>68</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>69</v>
       </c>
-      <c r="K4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
       <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>12844</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.12</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>771</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>70</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>71</v>
       </c>
-      <c r="K5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
       <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
         <v>60547</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>2513</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>72</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>73</v>
       </c>
-      <c r="K6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
       <c r="D7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
         <v>3028</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.12</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.5</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>91</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
       <c r="D8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>4190</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>180</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.8</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>74</v>
       </c>
-      <c r="K8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1455,23 +1489,23 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>1224</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.1</v>
       </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
       <c r="I9" t="s">
         <v>20</v>
       </c>
@@ -1479,570 +1513,576 @@
         <v>20</v>
       </c>
       <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
       <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
         <v>1206</v>
       </c>
-      <c r="F10">
-        <v>0.04</v>
-      </c>
       <c r="G10">
+        <v>0.04</v>
+      </c>
+      <c r="H10">
         <v>0.4</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>10</v>
-      </c>
-      <c r="I10">
-        <v>4.5</v>
       </c>
       <c r="J10">
         <v>4.5</v>
       </c>
-      <c r="K10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
-        <v>2</v>
-      </c>
       <c r="D11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1">
         <v>1149</v>
       </c>
-      <c r="F11">
-        <v>0.04</v>
-      </c>
       <c r="G11">
+        <v>0.04</v>
+      </c>
+      <c r="H11">
         <v>0.45</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>10</v>
-      </c>
-      <c r="I11">
-        <v>9.5</v>
       </c>
       <c r="J11">
         <v>9.5</v>
       </c>
-      <c r="K11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K11">
+        <v>9.5</v>
+      </c>
+      <c r="L11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
       <c r="D12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
         <v>6254</v>
       </c>
-      <c r="F12">
-        <v>0.04</v>
-      </c>
       <c r="G12">
+        <v>0.04</v>
+      </c>
+      <c r="H12">
         <v>0.5</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>63</v>
-      </c>
-      <c r="I12" t="s">
-        <v>75</v>
       </c>
       <c r="J12" t="s">
         <v>75</v>
       </c>
       <c r="K12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+      <c r="L12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
       <c r="D13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1">
         <v>12940</v>
       </c>
-      <c r="F13">
-        <v>0.04</v>
-      </c>
       <c r="G13">
+        <v>0.04</v>
+      </c>
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>259</v>
-      </c>
-      <c r="I13" t="s">
-        <v>76</v>
       </c>
       <c r="J13" t="s">
         <v>76</v>
       </c>
       <c r="K13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="L13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
-      <c r="C14" t="s">
-        <v>2</v>
-      </c>
       <c r="D14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>28967</v>
       </c>
-      <c r="F14">
-        <v>0.04</v>
-      </c>
       <c r="G14">
+        <v>0.04</v>
+      </c>
+      <c r="H14">
         <v>0.5</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>290</v>
-      </c>
-      <c r="I14">
-        <v>3.2</v>
       </c>
       <c r="J14">
         <v>3.2</v>
       </c>
-      <c r="K14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14">
+        <v>3.2</v>
+      </c>
+      <c r="L14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
       <c r="D15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>2545</v>
       </c>
-      <c r="F15">
-        <v>0.04</v>
-      </c>
       <c r="G15">
+        <v>0.04</v>
+      </c>
+      <c r="H15">
         <v>0.4</v>
       </c>
-      <c r="H15">
-        <v>20</v>
-      </c>
       <c r="I15">
-        <v>15.2</v>
+        <v>20</v>
       </c>
       <c r="J15">
         <v>15.2</v>
       </c>
-      <c r="K15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15">
+        <v>15.2</v>
+      </c>
+      <c r="L15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="C16" t="s">
-        <v>2</v>
-      </c>
       <c r="D16" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1">
         <v>75915</v>
       </c>
-      <c r="F16">
-        <v>0.04</v>
-      </c>
       <c r="G16">
+        <v>0.04</v>
+      </c>
+      <c r="H16">
         <v>0.48</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>729</v>
-      </c>
-      <c r="I16">
-        <v>7</v>
       </c>
       <c r="J16">
         <v>7</v>
       </c>
-      <c r="K16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K16">
+        <v>7</v>
+      </c>
+      <c r="L16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>27</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
-      <c r="C17" t="s">
-        <v>2</v>
-      </c>
       <c r="D17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1">
         <v>39822</v>
       </c>
-      <c r="F17">
-        <v>0.04</v>
-      </c>
       <c r="G17">
+        <v>0.04</v>
+      </c>
+      <c r="H17">
         <v>0.48</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>382</v>
-      </c>
-      <c r="I17" t="s">
-        <v>77</v>
       </c>
       <c r="J17" t="s">
         <v>77</v>
       </c>
       <c r="K17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="L17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>86</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
       <c r="D18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
         <v>12748</v>
       </c>
-      <c r="F18">
-        <v>0.04</v>
-      </c>
       <c r="G18">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="H18">
+        <v>0.45</v>
+      </c>
+      <c r="I18">
         <v>115</v>
-      </c>
-      <c r="I18">
-        <v>3.6</v>
       </c>
       <c r="J18">
         <v>3.6</v>
       </c>
-      <c r="K18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K18">
+        <v>3.6</v>
+      </c>
+      <c r="L18" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
-      <c r="C19" t="s">
-        <v>2</v>
-      </c>
       <c r="D19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19">
         <v>186</v>
       </c>
-      <c r="F19">
-        <v>0.04</v>
-      </c>
       <c r="G19">
+        <v>0.04</v>
+      </c>
+      <c r="H19">
         <v>0.5</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>1.9</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20" t="s">
         <v>81</v>
       </c>
-      <c r="C20" t="s">
-        <v>2</v>
-      </c>
       <c r="D20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1">
         <v>3053</v>
       </c>
-      <c r="F20">
-        <v>0.04</v>
-      </c>
       <c r="G20">
+        <v>0.04</v>
+      </c>
+      <c r="H20">
         <v>0.5</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>31</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>30</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
       <c r="D21" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
         <v>9165</v>
       </c>
-      <c r="F21">
-        <v>0.04</v>
-      </c>
       <c r="G21">
+        <v>0.04</v>
+      </c>
+      <c r="H21">
         <v>0.5</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>92</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>31</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
       <c r="D22" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1">
         <v>365617</v>
       </c>
-      <c r="F22">
-        <v>0.04</v>
-      </c>
       <c r="G22">
+        <v>0.04</v>
+      </c>
+      <c r="H22">
         <v>0.5</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>3656</v>
-      </c>
-      <c r="I22">
-        <v>93</v>
       </c>
       <c r="J22">
         <v>93</v>
       </c>
-      <c r="K22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K22">
+        <v>93</v>
+      </c>
+      <c r="L22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>32</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
-        <v>2</v>
-      </c>
       <c r="D23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="1">
         <v>25163</v>
       </c>
-      <c r="F23">
-        <v>0.04</v>
-      </c>
       <c r="G23">
+        <v>0.04</v>
+      </c>
+      <c r="H23">
         <v>0.48</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>242</v>
-      </c>
-      <c r="I23">
-        <v>11</v>
       </c>
       <c r="J23">
         <v>11</v>
       </c>
-      <c r="K23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K23">
+        <v>11</v>
+      </c>
+      <c r="L23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>33</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
       <c r="D24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1">
         <v>16417</v>
       </c>
-      <c r="F24">
-        <v>0.04</v>
-      </c>
       <c r="G24">
+        <v>0.04</v>
+      </c>
+      <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>164</v>
-      </c>
-      <c r="I24">
-        <v>23</v>
       </c>
       <c r="J24">
         <v>23</v>
       </c>
-      <c r="K24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K24">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>34</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
       </c>
-      <c r="C25" t="s">
-        <v>2</v>
-      </c>
       <c r="D25" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25">
         <v>361</v>
       </c>
-      <c r="F25">
-        <v>0.04</v>
-      </c>
       <c r="G25">
+        <v>0.04</v>
+      </c>
+      <c r="H25">
         <v>0.5</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>3.6</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2050,34 +2090,37 @@
         <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" t="s">
         <v>8</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>84</v>
       </c>
-      <c r="F26">
-        <v>0.04</v>
-      </c>
       <c r="G26">
+        <v>0.04</v>
+      </c>
+      <c r="H26">
         <v>0.5</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>0.8</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -2085,209 +2128,212 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27">
         <v>149</v>
       </c>
-      <c r="F27">
-        <v>0.04</v>
-      </c>
       <c r="G27">
+        <v>0.04</v>
+      </c>
+      <c r="H27">
         <v>0.4</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>1.2</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
-      <c r="K27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>87</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
       </c>
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
       <c r="D28" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28">
         <v>152</v>
       </c>
-      <c r="F28">
-        <v>0.04</v>
-      </c>
       <c r="G28">
+        <v>0.04</v>
+      </c>
+      <c r="H28">
         <v>0.5</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>1.5</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
-      <c r="K28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>37</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
       </c>
-      <c r="C29" t="s">
-        <v>2</v>
-      </c>
       <c r="D29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29">
         <v>645</v>
       </c>
-      <c r="F29">
-        <v>0.04</v>
-      </c>
       <c r="G29">
+        <v>0.04</v>
+      </c>
+      <c r="H29">
         <v>0.5</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>6.5</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
-      <c r="K29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>83</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
       </c>
-      <c r="C30" t="s">
-        <v>2</v>
-      </c>
       <c r="D30" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1">
         <v>1121</v>
       </c>
-      <c r="F30">
-        <v>0.04</v>
-      </c>
       <c r="G30">
+        <v>0.04</v>
+      </c>
+      <c r="H30">
         <v>0.5</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>11</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
-      <c r="K30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>38</v>
       </c>
       <c r="B31" t="s">
         <v>26</v>
       </c>
-      <c r="C31" t="s">
-        <v>2</v>
-      </c>
       <c r="D31" t="s">
-        <v>3</v>
-      </c>
-      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31">
         <v>119</v>
       </c>
-      <c r="F31">
-        <v>0.04</v>
-      </c>
       <c r="G31">
+        <v>0.04</v>
+      </c>
+      <c r="H31">
         <v>0.5</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>1.2</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
-      <c r="K31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>39</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
       </c>
-      <c r="C32" t="s">
-        <v>2</v>
-      </c>
       <c r="D32" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32">
         <v>885</v>
       </c>
-      <c r="F32">
-        <v>0.04</v>
-      </c>
       <c r="G32">
+        <v>0.04</v>
+      </c>
+      <c r="H32">
         <v>0.1</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>1.8</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2295,524 +2341,530 @@
         <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="1">
         <v>1158</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>0.08</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>0.1</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>78</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>79</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>42</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
       </c>
-      <c r="C34" t="s">
-        <v>2</v>
-      </c>
       <c r="D34" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1">
         <v>1384</v>
       </c>
-      <c r="F34">
-        <v>0.04</v>
-      </c>
       <c r="G34">
+        <v>0.04</v>
+      </c>
+      <c r="H34">
         <v>0.1</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>1.4</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>0.2</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>0</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>43</v>
       </c>
       <c r="B35" t="s">
         <v>26</v>
       </c>
-      <c r="C35" t="s">
-        <v>2</v>
-      </c>
       <c r="D35" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1">
         <v>2541</v>
       </c>
-      <c r="F35">
-        <v>0.04</v>
-      </c>
       <c r="G35">
+        <v>0.04</v>
+      </c>
+      <c r="H35">
         <v>0.3</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>15</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>1.4</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>1</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>84</v>
       </c>
       <c r="B36" t="s">
         <v>26</v>
       </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
       <c r="D36" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1">
         <v>11163</v>
       </c>
-      <c r="F36">
-        <v>0.04</v>
-      </c>
       <c r="G36">
+        <v>0.04</v>
+      </c>
+      <c r="H36">
         <v>0.5</v>
       </c>
-      <c r="H36" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
+      <c r="I36" t="s">
+        <v>20</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
-      <c r="K36" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>44</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
       </c>
-      <c r="C37" t="s">
-        <v>2</v>
-      </c>
       <c r="D37" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37">
         <v>35</v>
       </c>
-      <c r="F37">
-        <v>0.04</v>
-      </c>
       <c r="G37">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H37">
         <v>0.1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>45</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
-      <c r="C38" t="s">
-        <v>2</v>
-      </c>
       <c r="D38" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38">
         <v>585</v>
       </c>
-      <c r="F38">
-        <v>0.04</v>
-      </c>
       <c r="G38">
-        <v>0.45</v>
+        <v>0.04</v>
       </c>
       <c r="H38">
+        <v>0.5</v>
+      </c>
+      <c r="I38">
         <v>5.9</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
-      <c r="K38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38" t="s">
+        <v>4</v>
+      </c>
+      <c r="M38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>46</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
       </c>
-      <c r="C39" t="s">
-        <v>2</v>
-      </c>
       <c r="D39" t="s">
-        <v>3</v>
-      </c>
-      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="1">
         <v>13184</v>
       </c>
-      <c r="F39">
-        <v>0.04</v>
-      </c>
       <c r="G39">
+        <v>0.04</v>
+      </c>
+      <c r="H39">
         <v>0.5</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>132</v>
       </c>
-      <c r="I39" t="s">
-        <v>20</v>
-      </c>
       <c r="J39" t="s">
         <v>20</v>
       </c>
       <c r="K39" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>86</v>
       </c>
       <c r="B40" t="s">
         <v>18</v>
       </c>
-      <c r="C40" t="s">
-        <v>2</v>
-      </c>
       <c r="D40" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1">
         <v>1426</v>
       </c>
-      <c r="F40">
-        <v>0.04</v>
-      </c>
       <c r="G40">
+        <v>0.04</v>
+      </c>
+      <c r="H40">
         <v>0.5</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>14</v>
       </c>
-      <c r="I40" t="s">
-        <v>20</v>
-      </c>
       <c r="J40" t="s">
         <v>20</v>
       </c>
       <c r="K40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>28</v>
       </c>
       <c r="B41" t="s">
         <v>18</v>
       </c>
-      <c r="C41" t="s">
-        <v>2</v>
-      </c>
       <c r="D41" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="1">
         <v>2046</v>
       </c>
-      <c r="F41">
-        <v>0.04</v>
-      </c>
       <c r="G41">
+        <v>0.04</v>
+      </c>
+      <c r="H41">
         <v>0.5</v>
       </c>
-      <c r="H41">
-        <v>20</v>
-      </c>
-      <c r="I41" t="s">
-        <v>80</v>
+      <c r="I41">
+        <v>20</v>
       </c>
       <c r="J41" t="s">
         <v>80</v>
       </c>
       <c r="K41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+      <c r="L41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42" t="s">
         <v>18</v>
       </c>
-      <c r="C42" t="s">
-        <v>2</v>
-      </c>
       <c r="D42" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="1">
         <v>7362</v>
       </c>
-      <c r="F42">
-        <v>0.04</v>
-      </c>
       <c r="G42">
+        <v>0.04</v>
+      </c>
+      <c r="H42">
         <v>0.5</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>74</v>
-      </c>
-      <c r="I42" t="s">
-        <v>75</v>
       </c>
       <c r="J42" t="s">
         <v>75</v>
       </c>
       <c r="K42" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+      <c r="L42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43" t="s">
         <v>18</v>
       </c>
-      <c r="C43" t="s">
-        <v>2</v>
-      </c>
       <c r="D43" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1">
         <v>1691</v>
       </c>
-      <c r="F43">
-        <v>0.04</v>
-      </c>
       <c r="G43">
+        <v>0.04</v>
+      </c>
+      <c r="H43">
         <v>0.5</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>17</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
-      <c r="K43" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>30</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
       </c>
-      <c r="C44" t="s">
-        <v>2</v>
-      </c>
       <c r="D44" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1">
         <v>7078</v>
       </c>
-      <c r="F44">
-        <v>0.04</v>
-      </c>
       <c r="G44">
+        <v>0.04</v>
+      </c>
+      <c r="H44">
         <v>0.5</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>71</v>
       </c>
-      <c r="I44" t="s">
-        <v>20</v>
-      </c>
       <c r="J44" t="s">
         <v>20</v>
       </c>
       <c r="K44" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>85</v>
       </c>
       <c r="B45" t="s">
         <v>18</v>
       </c>
-      <c r="C45" t="s">
-        <v>2</v>
-      </c>
       <c r="D45" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1">
         <v>7917</v>
       </c>
-      <c r="F45">
-        <v>0.04</v>
-      </c>
       <c r="G45">
+        <v>0.04</v>
+      </c>
+      <c r="H45">
         <v>0.5</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>79</v>
       </c>
-      <c r="I45" t="s">
-        <v>20</v>
-      </c>
       <c r="J45" t="s">
         <v>20</v>
       </c>
       <c r="K45" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L45" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
         <v>18</v>
       </c>
-      <c r="C46" t="s">
-        <v>2</v>
-      </c>
       <c r="D46" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1">
         <v>1386</v>
       </c>
-      <c r="F46">
-        <v>0.04</v>
-      </c>
       <c r="G46">
+        <v>0.04</v>
+      </c>
+      <c r="H46">
         <v>0.5</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>14</v>
       </c>
-      <c r="I46" t="s">
-        <v>20</v>
-      </c>
       <c r="J46" t="s">
         <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
         <v>18</v>
       </c>
-      <c r="C47" t="s">
-        <v>2</v>
-      </c>
       <c r="D47" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47">
         <v>382</v>
       </c>
-      <c r="F47">
-        <v>0.04</v>
-      </c>
       <c r="G47">
+        <v>0.04</v>
+      </c>
+      <c r="H47">
         <v>0.5</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>3.8</v>
       </c>
-      <c r="I47" t="s">
-        <v>20</v>
-      </c>
       <c r="J47" t="s">
         <v>20</v>
       </c>
       <c r="K47" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -2820,338 +2872,338 @@
         <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48">
         <v>128</v>
       </c>
-      <c r="F48">
-        <v>0.04</v>
-      </c>
       <c r="G48">
+        <v>0.04</v>
+      </c>
+      <c r="H48">
         <v>0.45</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>1.2</v>
-      </c>
-      <c r="I48">
-        <v>1.6</v>
       </c>
       <c r="J48">
         <v>1.6</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48">
+        <v>1.6</v>
+      </c>
+      <c r="L48" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>34</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
       </c>
-      <c r="C49" t="s">
-        <v>2</v>
-      </c>
       <c r="D49" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="E49" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49">
         <v>250</v>
       </c>
-      <c r="F49">
-        <v>0.04</v>
-      </c>
       <c r="G49">
+        <v>0.04</v>
+      </c>
+      <c r="H49">
         <v>0.5</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>2.5</v>
       </c>
-      <c r="I49" t="s">
-        <v>20</v>
-      </c>
       <c r="J49" t="s">
         <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L49" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="B50" t="s">
         <v>18</v>
       </c>
-      <c r="C50" t="s">
-        <v>2</v>
-      </c>
       <c r="D50" t="s">
-        <v>3</v>
-      </c>
-      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" t="s">
+        <v>3</v>
+      </c>
+      <c r="F50" s="1">
         <v>5986</v>
       </c>
-      <c r="F50">
-        <v>0.04</v>
-      </c>
       <c r="G50">
+        <v>0.04</v>
+      </c>
+      <c r="H50">
         <v>0.5</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>60</v>
-      </c>
-      <c r="I50">
-        <v>0.8</v>
       </c>
       <c r="J50">
         <v>0.8</v>
       </c>
-      <c r="K50" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K50">
+        <v>0.8</v>
+      </c>
+      <c r="L50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>88</v>
       </c>
       <c r="B51" t="s">
         <v>18</v>
       </c>
-      <c r="C51" t="s">
-        <v>2</v>
-      </c>
       <c r="D51" t="s">
-        <v>3</v>
-      </c>
-      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+      <c r="E51" t="s">
+        <v>3</v>
+      </c>
+      <c r="F51" s="1">
         <v>1204</v>
       </c>
-      <c r="F51">
-        <v>0.04</v>
-      </c>
       <c r="G51">
+        <v>0.04</v>
+      </c>
+      <c r="H51">
         <v>0.5</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>9.6</v>
-      </c>
-      <c r="I51">
-        <v>0.8</v>
       </c>
       <c r="J51">
         <v>0.8</v>
       </c>
-      <c r="K51" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K51">
+        <v>0.8</v>
+      </c>
+      <c r="L51" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>53</v>
       </c>
       <c r="B52" t="s">
         <v>18</v>
       </c>
-      <c r="C52" t="s">
-        <v>2</v>
-      </c>
       <c r="D52" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="E52" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52">
         <v>371</v>
       </c>
-      <c r="F52">
-        <v>0.04</v>
-      </c>
       <c r="G52">
+        <v>0.04</v>
+      </c>
+      <c r="H52">
         <v>0.5</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>3.7</v>
       </c>
-      <c r="I52" t="s">
-        <v>20</v>
-      </c>
       <c r="J52" t="s">
         <v>20</v>
       </c>
       <c r="K52" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L52" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>83</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
       </c>
-      <c r="C53" t="s">
-        <v>2</v>
-      </c>
       <c r="D53" t="s">
-        <v>3</v>
-      </c>
-      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" t="s">
+        <v>3</v>
+      </c>
+      <c r="F53" s="1">
         <v>6919</v>
       </c>
-      <c r="F53">
-        <v>0.04</v>
-      </c>
       <c r="G53">
+        <v>0.04</v>
+      </c>
+      <c r="H53">
         <v>0.5</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>69</v>
       </c>
-      <c r="I53" t="s">
-        <v>20</v>
-      </c>
       <c r="J53" t="s">
         <v>20</v>
       </c>
       <c r="K53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L53" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>54</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
       </c>
-      <c r="C54" t="s">
-        <v>2</v>
-      </c>
       <c r="D54" t="s">
-        <v>3</v>
-      </c>
-      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="1">
         <v>4082</v>
       </c>
-      <c r="F54">
-        <v>0.04</v>
-      </c>
       <c r="G54">
+        <v>0.04</v>
+      </c>
+      <c r="H54">
         <v>0.5</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>41</v>
       </c>
-      <c r="I54" t="s">
-        <v>20</v>
-      </c>
       <c r="J54" t="s">
         <v>20</v>
       </c>
       <c r="K54" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L54" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>55</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
-      <c r="C55" t="s">
-        <v>2</v>
-      </c>
       <c r="D55" t="s">
-        <v>3</v>
-      </c>
-      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" t="s">
+        <v>3</v>
+      </c>
+      <c r="F55" s="1">
         <v>11555</v>
       </c>
-      <c r="F55">
-        <v>0.04</v>
-      </c>
       <c r="G55">
+        <v>0.04</v>
+      </c>
+      <c r="H55">
         <v>0.5</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>116</v>
       </c>
-      <c r="I55" t="s">
-        <v>20</v>
-      </c>
       <c r="J55" t="s">
         <v>20</v>
       </c>
       <c r="K55" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L55" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>39</v>
       </c>
       <c r="B56" t="s">
         <v>18</v>
       </c>
-      <c r="C56" t="s">
-        <v>2</v>
-      </c>
       <c r="D56" t="s">
-        <v>3</v>
-      </c>
-      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+      <c r="E56" t="s">
+        <v>3</v>
+      </c>
+      <c r="F56" s="1">
         <v>5531</v>
       </c>
-      <c r="F56">
-        <v>0.04</v>
-      </c>
       <c r="G56">
+        <v>0.04</v>
+      </c>
+      <c r="H56">
         <v>0.1</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>11</v>
       </c>
-      <c r="I56" t="s">
-        <v>20</v>
-      </c>
       <c r="J56" t="s">
         <v>20</v>
       </c>
       <c r="K56" t="s">
+        <v>20</v>
+      </c>
+      <c r="L56" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>42</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
       </c>
-      <c r="C57" t="s">
-        <v>2</v>
-      </c>
       <c r="D57" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>20</v>
-      </c>
-      <c r="F57">
-        <v>0.04</v>
+        <v>3</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
       </c>
       <c r="G57">
+        <v>0.04</v>
+      </c>
+      <c r="H57">
         <v>0.1</v>
       </c>
-      <c r="H57" t="s">
-        <v>20</v>
-      </c>
       <c r="I57" t="s">
         <v>20</v>
       </c>
@@ -3159,104 +3211,104 @@
         <v>20</v>
       </c>
       <c r="K57" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>43</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
       </c>
-      <c r="C58" t="s">
-        <v>2</v>
-      </c>
       <c r="D58" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="E58" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58">
         <v>101</v>
       </c>
-      <c r="F58">
-        <v>0.04</v>
-      </c>
       <c r="G58">
+        <v>0.04</v>
+      </c>
+      <c r="H58">
         <v>0.1</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>0.2</v>
       </c>
-      <c r="I58" t="s">
-        <v>20</v>
-      </c>
       <c r="J58" t="s">
         <v>20</v>
       </c>
       <c r="K58" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>44</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
       </c>
-      <c r="C59" t="s">
-        <v>2</v>
-      </c>
       <c r="D59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59">
         <v>37</v>
       </c>
-      <c r="F59">
-        <v>0.04</v>
-      </c>
       <c r="G59">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H59">
         <v>0.1</v>
       </c>
-      <c r="I59" t="s">
-        <v>20</v>
+      <c r="I59">
+        <v>0.1</v>
       </c>
       <c r="J59" t="s">
         <v>20</v>
       </c>
       <c r="K59" t="s">
+        <v>20</v>
+      </c>
+      <c r="L59" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>45</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
       </c>
-      <c r="C60" t="s">
-        <v>2</v>
-      </c>
       <c r="D60" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>20</v>
-      </c>
-      <c r="F60">
-        <v>0.04</v>
+        <v>3</v>
+      </c>
+      <c r="F60" t="s">
+        <v>20</v>
       </c>
       <c r="G60">
+        <v>0.04</v>
+      </c>
+      <c r="H60">
         <v>0.5</v>
       </c>
-      <c r="H60" t="s">
-        <v>20</v>
-      </c>
       <c r="I60" t="s">
         <v>20</v>
       </c>
@@ -3264,41 +3316,44 @@
         <v>20</v>
       </c>
       <c r="K60" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L60" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>84</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
       </c>
-      <c r="C61" t="s">
-        <v>2</v>
-      </c>
       <c r="D61" t="s">
-        <v>3</v>
-      </c>
-      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="E61" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61">
         <v>373</v>
       </c>
-      <c r="F61">
-        <v>0.04</v>
-      </c>
       <c r="G61">
+        <v>0.04</v>
+      </c>
+      <c r="H61">
         <v>0.5</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>3.7</v>
       </c>
-      <c r="I61" t="s">
-        <v>20</v>
-      </c>
       <c r="J61" t="s">
         <v>20</v>
       </c>
       <c r="K61" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61" t="s">
         <v>4</v>
       </c>
     </row>
